--- a/tests/产品决策卡-核心指标表.xlsx
+++ b/tests/产品决策卡-核心指标表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="128">
   <si>
     <t>决策卡：综合显示</t>
   </si>
@@ -140,15 +140,6 @@
   </si>
   <si>
     <t>信任锚——无名的店不敢合作</t>
-  </si>
-  <si>
-    <t>supplier.tpYear</t>
-  </si>
-  <si>
-    <t>平台入驻年限</t>
-  </si>
-  <si>
-    <t>印尼卖家：“1年新店不敢合作”，和价格同等重要</t>
   </si>
   <si>
     <t>supplier.stats.positiveReviewRate</t>
@@ -405,6 +396,12 @@
   </si>
   <si>
     <t>重复(综合区)，信任起点</t>
+  </si>
+  <si>
+    <t>supplier.tpYear</t>
+  </si>
+  <si>
+    <t>平台入驻年限</t>
   </si>
   <si>
     <t>印尼卖家判断稳定性的第一指标</t>
@@ -1246,6 +1243,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1253,9 +1253,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1792,7 +1789,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="43.7272727272727" defaultRowHeight="35" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.4545454545455" customWidth="1"/>
@@ -1931,554 +1928,537 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="8">
-        <v>38725</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>33</v>
+      <c r="E9" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" customHeight="1" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="6" t="s">
         <v>48</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="C13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="10" t="s">
         <v>52</v>
       </c>
+      <c r="B14" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="C14" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:5">
+      <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
+      <c r="E17" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="6" t="s">
         <v>65</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="C19" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="10" t="s">
         <v>69</v>
       </c>
+      <c r="B20" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="C20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="6" t="s">
         <v>77</v>
+      </c>
+      <c r="B22" s="6">
+        <v>3505</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="4" t="s">
+    <row r="24" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="6">
-        <v>3505</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="6" t="s">
+    </row>
+    <row r="27" customHeight="1" spans="1:5">
+      <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A25" s="1" t="s">
+      <c r="B27" s="9">
+        <v>38725</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="10" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:5">
+      <c r="A29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="8">
-        <v>38725</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="C29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="E29" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:5">
+      <c r="A30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:5">
+      <c r="A32" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="13" t="s">
-        <v>92</v>
+      <c r="E32" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="A33" s="4" t="s">
         <v>96</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>98</v>
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:5">
       <c r="A37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="C37" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="A42" s="13" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="13" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" display="https://cbu01.alicdn.com/…" tooltip="https://cbu01.alicdn.com/%E2%80%A6"/>
-    <hyperlink ref="B15" r:id="rId2" display="detail.1688.com/offer/..." tooltip="https://detail.1688.com/offer/"/>
-    <hyperlink ref="B34" r:id="rId3" display="r.1688.com/auth/..." tooltip="https://r.1688.com/auth/"/>
-    <hyperlink ref="B41" r:id="rId4" display="winport.m.1688.com/..." tooltip="https://winport.m.1688.com/"/>
+    <hyperlink ref="B14" r:id="rId2" display="detail.1688.com/offer/..." tooltip="https://detail.1688.com/offer/"/>
+    <hyperlink ref="B33" r:id="rId3" display="r.1688.com/auth/..." tooltip="https://r.1688.com/auth/"/>
+    <hyperlink ref="B40" r:id="rId4" display="winport.m.1688.com/..." tooltip="https://winport.m.1688.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
